--- a/チーム開発詳細設計.xlsx
+++ b/チーム開発詳細設計.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tnoma\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B6B43C-670A-442B-88EA-5968D05C7084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63E4AE1-3BBA-4919-9001-50293FC9413A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C17CAFEF-67A7-4D51-A7FF-9940DF7CD199}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C17CAFEF-67A7-4D51-A7FF-9940DF7CD199}"/>
   </bookViews>
   <sheets>
     <sheet name="画面イメージ" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Folder Structure</t>
   </si>
@@ -36,9 +36,6 @@
   </si>
   <si>
     <t>/Pages</t>
-  </si>
-  <si>
-    <t>/Todos</t>
   </si>
   <si>
     <t>/Models</t>
@@ -517,14 +514,6 @@
   </si>
   <si>
     <t>1000文字以内しか入力欄に入らない</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>サーバーサイド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>C#</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -719,12 +708,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -739,9 +722,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -762,6 +742,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1102,11 +1091,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>549302</xdr:colOff>
+      <xdr:colOff>543441</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>221642</xdr:rowOff>
+      <xdr:rowOff>157165</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1380634" cy="328360"/>
+    <xdr:ext cx="1521699" cy="328360"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="テキスト ボックス 4">
@@ -1120,8 +1109,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7241650" y="453555"/>
-          <a:ext cx="1380634" cy="328360"/>
+          <a:off x="1879872" y="385765"/>
+          <a:ext cx="1521699" cy="328360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1172,7 +1161,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>新規登録機能</a:t>
+            <a:t>新規登録ボタン</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
@@ -1580,7 +1569,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>622853</xdr:colOff>
+      <xdr:colOff>630473</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>212035</xdr:rowOff>
     </xdr:from>
@@ -1598,7 +1587,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8653670" y="1371600"/>
+          <a:off x="3297473" y="1347708"/>
           <a:ext cx="408638" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1632,7 +1621,6 @@
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
             <a:t>edit</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1835,6 +1823,186 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>558324</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>178676</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1031051" cy="328360"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61D7558D-C52A-B10E-C7BA-378C3BD0458B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3899401" y="407276"/>
+          <a:ext cx="1031051" cy="328360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>新規登録画面</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609344</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>93531</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>543084</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>139913</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{418308C3-58E0-2590-1C4F-377C4EC59627}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3282206" y="550731"/>
+          <a:ext cx="601955" cy="46382"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>455415</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57342</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1313180" cy="328423"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E736819B-2B08-1218-F16A-1C8BB42BBB67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3796492" y="57342"/>
+          <a:ext cx="1313180" cy="328423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ポップアップ表示</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1844,7 +2012,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3298384</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>179650</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1254382" cy="328423"/>
@@ -1916,7 +2084,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3279251</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1413592" cy="328423"/>
@@ -2287,265 +2455,229 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD1F112-5F81-400D-9002-BA2683B2CA98}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="63.3984375" customWidth="1"/>
     <col min="3" max="3" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="34.799999999999997" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.45">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="18"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.45">
-      <c r="B2" s="11" t="s">
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="B2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="16.8" x14ac:dyDescent="0.45">
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="13" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="13"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="14" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="13"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="14" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="14" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="14" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="14" t="s">
-        <v>12</v>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="10" t="s">
+        <v>3</v>
       </c>
       <c r="B12" s="13"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="14" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="14" t="s">
-        <v>14</v>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="14" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="13" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="14" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2571,132 +2703,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="20" spans="6:9" x14ac:dyDescent="0.45">
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
@@ -2731,8 +2863,8 @@
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="6:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
       <c r="H26" s="1"/>
     </row>
     <row r="27" spans="6:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45"/>
